--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487562_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487562_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9782</v>
+        <v>3.2748</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7539</v>
+        <v>1.8367</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2243</v>
+        <v>1.4381</v>
       </c>
       <c r="G2" t="n">
         <v>3.0884</v>
@@ -610,13 +610,13 @@
         <v>2.7419</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5607</v>
+        <v>-0.2641</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6358</v>
+        <v>0.447</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.7111</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3329</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7695</v>
+        <v>0.9033</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1565</v>
+        <v>2.3973</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.387</v>
+        <v>-1.4939</v>
       </c>
       <c r="G3" t="n">
         <v>-1.1905</v>
@@ -688,13 +688,13 @@
         <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8597</v>
+        <v>-0.0065</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3803</v>
+        <v>0.6211</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5206</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>2.1003</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. TOMIC</t>
+          <t>S. MARTINEZ GRANDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2047</v>
+        <v>0.8207</v>
       </c>
       <c r="E4" t="n">
-        <v>3.806</v>
+        <v>2.5943</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6013</v>
+        <v>-1.7736</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5609</v>
+        <v>0.9498</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0314</v>
+        <v>1.7384</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4705</v>
+        <v>-0.7887</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8317</v>
+        <v>1.68</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3678</v>
+        <v>2.3477</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4638</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2708</v>
+        <v>-0.7302</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3364</v>
+        <v>-0.6093</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9344</v>
+        <v>-0.1209</v>
       </c>
       <c r="P4" t="n">
         <v>0.5875</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5483</v>
+        <v>0.6602</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9744</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4261</v>
+        <v>-0.0168</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.492</v>
+        <v>-1.3768</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.492</v>
+        <v>-2.5934</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GRANDA</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3031</v>
+        <v>0.3265</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0232</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7201</v>
+        <v>0.2541</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9498</v>
+        <v>0.6231</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7384</v>
+        <v>-0.1096</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7887</v>
+        <v>0.7327</v>
       </c>
       <c r="J5" t="n">
-        <v>1.68</v>
+        <v>1.0252</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3477</v>
+        <v>0.2977</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6677999999999999</v>
+        <v>0.7275</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7302</v>
+        <v>-0.4021</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6093</v>
+        <v>-0.4073</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1209</v>
+        <v>0.0052</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1426</v>
+        <v>-0.4924</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1059</v>
+        <v>0.0265</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0367</v>
+        <v>-0.5189</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3768</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.5934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>M. TOMIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1426</v>
+        <v>-0.2593</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1917</v>
+        <v>2.4757</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3343</v>
+        <v>-2.735</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6231</v>
+        <v>0.5609</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1096</v>
+        <v>1.0314</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7327</v>
+        <v>-0.4705</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0252</v>
+        <v>1.8317</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2977</v>
+        <v>1.3678</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7275</v>
+        <v>0.4638</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4021</v>
+        <v>-1.2708</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4073</v>
+        <v>-0.3364</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0052</v>
+        <v>-0.9344</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6763</v>
+        <v>0.0842</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2376</v>
+        <v>0.644</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4387</v>
+        <v>-0.5598</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2606</v>
+        <v>-0.9698</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9692</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2914</v>
+        <v>-0.2647</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4148</v>
@@ -1000,13 +1000,13 @@
         <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.825</v>
+        <v>-0.5342</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.297</v>
+        <v>-0.0329</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.528</v>
+        <v>-0.5012</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4918</v>
+        <v>-1.0345</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4921</v>
+        <v>2.3817</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0004</v>
+        <v>-3.4162</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3299</v>
+        <v>3.2201</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5524</v>
+        <v>0.7704</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2225</v>
+        <v>2.4497</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0128</v>
+        <v>4.9617</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1941</v>
+        <v>1.3099</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2069</v>
+        <v>3.6518</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3427</v>
+        <v>-1.7416</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3582</v>
+        <v>-0.5395</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0156</v>
+        <v>-1.2021</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7834</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1543</v>
+        <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2874</v>
+        <v>-0.5875</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2151</v>
+        <v>-0.2506</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0723</v>
+        <v>-0.337</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6659</v>
+        <v>-2.1003</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2178</v>
+        <v>0.6083</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8837</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>M. GARCIA FRAGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.645</v>
+        <v>-1.5436</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2581</v>
+        <v>-1.1906</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3869</v>
+        <v>-0.3529</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9512</v>
+        <v>0.0052</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2345</v>
+        <v>-0.475</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2833</v>
+        <v>0.4802</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5001</v>
+        <v>0.8667</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6262</v>
+        <v>0.1344</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1261</v>
+        <v>0.7323</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4511</v>
+        <v>-0.8615</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6083</v>
+        <v>-0.6093</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1572</v>
+        <v>-0.2521</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>2.546</v>
+        <v>2.3502</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3976</v>
+        <v>-0.1156</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5921999999999999</v>
+        <v>-0.0988</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9899</v>
+        <v>-0.0168</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8837</v>
+        <v>-1.8249</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.492</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8572</v>
+        <v>-1.6077</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3995</v>
+        <v>-1.301</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4576</v>
+        <v>-0.3067</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4286</v>
+        <v>-0.9512</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1657</v>
+        <v>-1.2345</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2629</v>
+        <v>0.2833</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8068</v>
+        <v>-0.5001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6856</v>
+        <v>-0.6262</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1212</v>
+        <v>0.1261</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6218</v>
+        <v>-0.4511</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4802</v>
+        <v>-0.6083</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1416</v>
+        <v>0.1572</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1751</v>
+        <v>2.546</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3445</v>
+        <v>-0.3604</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0851</v>
+        <v>0.5493</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4296</v>
+        <v>-0.9097</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1578</v>
+        <v>-0.8837</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3329</v>
+        <v>0.6083</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8249</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9126</v>
+        <v>-2.0464</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5036</v>
+        <v>-2.0467</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4162</v>
+        <v>0.0004</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2201</v>
+        <v>-1.3299</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7704</v>
+        <v>-1.5524</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4497</v>
+        <v>0.2225</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9617</v>
+        <v>0.0128</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3099</v>
+        <v>-0.1941</v>
       </c>
       <c r="L11" t="n">
-        <v>3.6518</v>
+        <v>0.2069</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7416</v>
+        <v>-1.3427</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5395</v>
+        <v>-1.3582</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2021</v>
+        <v>0.0156</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5668</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3709</v>
+        <v>2.1543</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4656</v>
+        <v>0.7328</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1286</v>
+        <v>0.6605</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.337</v>
+        <v>0.0723</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1003</v>
+        <v>-0.6659</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6083</v>
+        <v>0.2178</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7086</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. GARCIA FRAGA</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1635</v>
+        <v>-2.2025</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8641</v>
+        <v>-0.8518</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2995</v>
+        <v>-1.3507</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0052</v>
+        <v>1.4286</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.475</v>
+        <v>1.1657</v>
       </c>
       <c r="I12" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8068</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6856</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.6218</v>
+      </c>
+      <c r="N12" t="n">
         <v>0.4802</v>
       </c>
-      <c r="J12" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.1344</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.7323</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-0.8615</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-0.6093</v>
-      </c>
       <c r="O12" t="n">
-        <v>-0.2521</v>
+        <v>0.1416</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3917</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7355</v>
+        <v>-0.6899</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7722</v>
+        <v>0.6328</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0367</v>
+        <v>-1.3227</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8249</v>
+        <v>-2.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X12" t="n">
         <v>-1.8249</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9326</v>
+        <v>-4.338500000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.068499999999998</v>
+        <v>5.662900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.001</v>
+        <v>-10.0011</v>
       </c>
       <c r="G13" t="n">
         <v>4.9897</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3435999999999998</v>
+        <v>0.3435999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>4.646000000000001</v>
+        <v>4.646</v>
       </c>
       <c r="J13" t="n">
         <v>15.3281</v>
@@ -1447,7 +1447,7 @@
         <v>7.4526</v>
       </c>
       <c r="L13" t="n">
-        <v>7.875300000000001</v>
+        <v>7.8753</v>
       </c>
       <c r="M13" t="n">
         <v>-10.3385</v>
@@ -1459,7 +1459,7 @@
         <v>-3.2295</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9790000000000001</v>
+        <v>0.979</v>
       </c>
       <c r="Q13" t="n">
         <v>-17.6263</v>
@@ -1468,16 +1468,16 @@
         <v>18.6055</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1672</v>
+        <v>-1.5734</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2818</v>
+        <v>3.8758</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.4491</v>
+        <v>-5.4492</v>
       </c>
       <c r="V13" t="n">
-        <v>-8.734</v>
+        <v>-8.733999999999998</v>
       </c>
       <c r="W13" t="n">
         <v>4.0855</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>J. ABELLEIRA MARTINEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5346</v>
+        <v>3.3359</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3717</v>
+        <v>3.7011</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1629</v>
+        <v>-0.3652</v>
       </c>
       <c r="G14" t="n">
-        <v>0.993</v>
+        <v>-0.8549</v>
       </c>
       <c r="H14" t="n">
-        <v>0.851</v>
+        <v>-0.8497</v>
       </c>
       <c r="I14" t="n">
-        <v>0.142</v>
+        <v>-0.0052</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1743</v>
+        <v>1.8815</v>
       </c>
       <c r="K14" t="n">
-        <v>1.053</v>
+        <v>0.847</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1212</v>
+        <v>1.0345</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1813</v>
+        <v>-2.7364</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2021</v>
+        <v>-1.6968</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0208</v>
+        <v>-1.0397</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1751</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1958</v>
+        <v>-2.9377</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3709</v>
+        <v>2.9377</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9173</v>
+        <v>0.1991</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3933</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.524</v>
+        <v>-0.6331</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5507</v>
+        <v>3.9918</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.9252</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5507</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. ACEVEDO VASQUEZ</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9756</v>
+        <v>2.802</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1441</v>
+        <v>2.5077</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1685</v>
+        <v>0.2943</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1132</v>
+        <v>2.574</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1885</v>
+        <v>1.1443</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0753</v>
+        <v>1.4297</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3632</v>
+        <v>2.2324</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5905</v>
+        <v>0.9391</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7727000000000001</v>
+        <v>1.2933</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.25</v>
+        <v>0.3416</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4021</v>
+        <v>0.2052</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.848</v>
+        <v>0.1364</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.0921</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1336</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9882</v>
+        <v>-0.0473</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2231</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2349</v>
+        <v>-0.0473</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8327</v>
+        <v>0.2754</v>
       </c>
       <c r="W15" t="n">
-        <v>3.6498</v>
+        <v>0.2754</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7486</v>
+        <v>2.5003</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5077</v>
+        <v>1.6554</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2408</v>
+        <v>0.8449</v>
       </c>
       <c r="G16" t="n">
-        <v>2.574</v>
+        <v>0.993</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1443</v>
+        <v>0.851</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4297</v>
+        <v>0.142</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2324</v>
+        <v>1.1743</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9391</v>
+        <v>1.053</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2933</v>
+        <v>0.1212</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3416</v>
+        <v>-0.1813</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2052</v>
+        <v>-0.2021</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1364</v>
+        <v>0.0208</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1008</v>
+        <v>0.8829</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1008</v>
+        <v>0.206</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2754</v>
+        <v>-0.5507</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ABELLEIRA MARTINEZ</t>
+          <t>D. MARTIN MACEIRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,37 +1735,37 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0157</v>
+        <v>2.3139</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6778</v>
+        <v>1.4763</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.662</v>
+        <v>0.8376</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8549</v>
+        <v>-1.2656</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8497</v>
+        <v>2.4529</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0052</v>
+        <v>-3.7186</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8815</v>
+        <v>0.7219</v>
       </c>
       <c r="K17" t="n">
-        <v>0.847</v>
+        <v>3.4008</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0345</v>
+        <v>-2.6789</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7364</v>
+        <v>-1.9875</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6968</v>
+        <v>-0.9479</v>
       </c>
       <c r="O17" t="n">
         <v>-1.0397</v>
@@ -1774,25 +1774,25 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9377</v>
+        <v>-3.1336</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9377</v>
+        <v>3.1336</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1211</v>
+        <v>0.2536</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1911</v>
+        <v>0.6287</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.93</v>
+        <v>-0.3751</v>
       </c>
       <c r="V17" t="n">
-        <v>3.9918</v>
+        <v>3.3259</v>
       </c>
       <c r="W17" t="n">
-        <v>3.9252</v>
+        <v>3.2593</v>
       </c>
       <c r="X17" t="n">
         <v>0.06660000000000001</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MARTIN MACEIRA</t>
+          <t>R. ACEVEDO VASQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1579</v>
+        <v>2.0574</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9646</v>
+        <v>2.2231</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1932</v>
+        <v>-0.1657</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2656</v>
+        <v>0.1132</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4529</v>
+        <v>1.1885</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.7186</v>
+        <v>-1.0753</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7219</v>
+        <v>2.3632</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4008</v>
+        <v>1.5905</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.6789</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9875</v>
+        <v>-2.25</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9479</v>
+        <v>-0.4021</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0397</v>
+        <v>-1.848</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1336</v>
+        <v>-5.0921</v>
       </c>
       <c r="R18" t="n">
         <v>3.1336</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9024</v>
+        <v>1.07</v>
       </c>
       <c r="T18" t="n">
-        <v>0.117</v>
+        <v>1.3021</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0194</v>
+        <v>-0.2322</v>
       </c>
       <c r="V18" t="n">
-        <v>3.3259</v>
+        <v>2.8327</v>
       </c>
       <c r="W18" t="n">
-        <v>3.2593</v>
+        <v>3.6498</v>
       </c>
       <c r="X18" t="n">
-        <v>0.06660000000000001</v>
+        <v>-0.8171</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1237</v>
+        <v>1.1726</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1787</v>
+        <v>1.281</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0549</v>
+        <v>-0.1084</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0439</v>
@@ -1936,13 +1936,13 @@
         <v>1.7626</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3384</v>
+        <v>0.3873</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3435</v>
+        <v>0.4458</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0051</v>
+        <v>-0.0585</v>
       </c>
       <c r="V19" t="n">
         <v>0.06660000000000001</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.04</v>
+        <v>-0.7361</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5294</v>
+        <v>-1.0411</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5695</v>
+        <v>0.305</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2123</v>
@@ -2014,13 +2014,13 @@
         <v>2.7419</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1936</v>
+        <v>0.4174</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2327</v>
+        <v>0.721</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0391</v>
+        <v>-0.3036</v>
       </c>
       <c r="V20" t="n">
         <v>0.2754</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8886</v>
+        <v>-1.5502</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2861</v>
+        <v>-1.0814</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6025</v>
+        <v>-0.4688</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1512</v>
@@ -2092,13 +2092,13 @@
         <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4632</v>
+        <v>-0.1248</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4158</v>
+        <v>-0.2111</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0473</v>
+        <v>0.0863</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6659</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6093</v>
+        <v>-2.4848</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0124</v>
+        <v>-0.8077</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5969</v>
+        <v>-1.6771</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1289</v>
@@ -2170,13 +2170,13 @@
         <v>0.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2846</v>
+        <v>-0.1601</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0176</v>
+        <v>0.2223</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3022</v>
+        <v>-0.3824</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6083</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1659</v>
+        <v>-3.7963</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8993</v>
+        <v>-0.797</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2666</v>
+        <v>-2.9993</v>
       </c>
       <c r="G23" t="n">
         <v>-1.013</v>
@@ -2248,13 +2248,13 @@
         <v>1.5668</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3982</v>
+        <v>-0.0285</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7287</v>
+        <v>0.831</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1269</v>
+        <v>-0.8596</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2088</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.932299999999999</v>
+        <v>5.614699999999999</v>
       </c>
       <c r="E24" t="n">
         <v>9.1174</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.185</v>
+        <v>-3.5027</v>
       </c>
       <c r="G24" t="n">
         <v>-4.9896</v>
@@ -2311,7 +2311,7 @@
         <v>-15.328</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.452800000000001</v>
+        <v>-7.4528</v>
       </c>
       <c r="O24" t="n">
         <v>-7.875500000000001</v>
@@ -2326,13 +2326,13 @@
         <v>17.6263</v>
       </c>
       <c r="S24" t="n">
-        <v>2.1672</v>
+        <v>2.8496</v>
       </c>
       <c r="T24" t="n">
-        <v>5.449</v>
+        <v>5.4489</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.2817</v>
+        <v>-2.5995</v>
       </c>
       <c r="V24" t="n">
         <v>8.7341</v>
